--- a/news_daily/2026-08-28.xlsx
+++ b/news_daily/2026-08-28.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -89,10 +89,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH24"/>
+  <dimension ref="A1:BL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,6 +833,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -864,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -925,7 +953,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -934,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>986f34666ab040caa096f9e953d0a0db</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>68ad01e8a08fd53f75f1b48d</t>
@@ -955,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -991,338 +1027,382 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>TJX</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>TJX Companies</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T23:15:59+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Tariff refunds lift TJX (NYSE: TJX) profit and Q2 EPS</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>關稅</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>'-0.13</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOVmJ5cXhRSGdVRDlnTDN1bGFtTWxpSlBVUVYwc0MyVUZyYVVXMTRyYzZMa0Fub1NXMmxtTFd6VjR6TFlNOXA2cUlDemRDYkdIcWtaa0tCU2o0LXV4dFpSRnE5WV9hd2FUVnhxWEstMGQxRC1WTU9vUFNIU2sycmFHMW03RDl1Z3ZRNjhUWmJ6cVhBVS1RR0NPWF9TVnoyZGJMWFV3T0VOS3NMZ1hPSHBnUXl3?oc=5</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Stock Titan</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>TARIFF</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>12d92439e62c23b1475061c7</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>7c4c86bfa31dbcfac542a4d2</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
         <is>
           <t>TJX</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr"/>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-08-28T22:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>City of Carson reaches $370M settlement with Marathon Petroleum</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>0.301</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNclNwYXl4c3VkNkhYQl84U2xGdUJabjVwRDlfOFpFQkhWN2lUSEIzTVhFdHR6LWtrTWhlNi1zQ3ZlaVVTc3pCUW9rLVdZdWdJaUJEcGtZTW1iLVE0ZVM5T0VoZnFaNmdBcnFwenNscnNzMzFEaXVZM0tNb0NBbFVYUUlYY2I4a2NpV0Ntb212UnFnSG5QLUtKYw?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Spectrum News</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>6e0f237ed05e49f7865b0256850bb1ce</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>5978c63699fa1e8a80ba9dfa</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>33d08b065a42e209c66e2bae</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.301</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNclNwYXl4c3VkNkhYQl84U2xGdUJabjVwRDlfOFpFQkhWN2lUSEIzTVhFdHR6LWtrTWhlNi1zQ3ZlaVVTc3pCUW9rLVdZdWdJaUJEcGtZTW1iLVE0ZVM5T0VoZnFaNmdBcnFwenNscnNzMzFEaXVZM0tNb0NBbFVYUUlYY2I4a2NpV0Ntb212UnFnSG5QLUtKYw?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Spectrum News</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>5978c63699fa1e8a80ba9dfa</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>33d08b065a42e209c66e2bae</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1358,28 +1438,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1419,7 +1503,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1428,7 +1512,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>35e900ff3ecd43eaa6d03cf7cd87d342</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>11429a7f0a6964d43a66935e</t>
@@ -1449,7 +1537,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1485,6 +1577,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1655,346 +1763,358 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>WDAY</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Workday, Inc.</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T19:28:23+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>WDAY Stock Downgraded Despite Q2 Beat – Analysts Flag Risk Of Another ‘Guide Down’</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>'-0.937</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZDZ5QzhHbmlzTUUxbXo3ejRjY2JnRTgyc2plNG1CN25hSnNxcG5YSTNNU1NaMVllVkRjU2Q4U2F6UFp6dHUybU11VWVPcVk2VEZkeV84NjR6UGZLM1lLbEhtVkJ3NE1VTGhiX0FoVUZsTmI4QkwySWY5VGlEV3FmQTRUcngxbU5uYWozTjF0VjZhblFKTXhqRWg5VTdfZw?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>59f6e258cf159c82c3472ab9</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>089e057a00f94dfac6f4f7c4</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>WDAY</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>ADSK</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Autodesk, Inc.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T18:36:05+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Autodesk shares fall as fiscal 2027 earnings guidance trails expectations despite Q2 beat</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>'-0.962</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQY1BfMFdYRnhLRVZGQ1MwbHNNaDJueWdMc1dPSnd0NWV4NlRSV1Q0czRtRmdvNjJQY1pJNzVpcXlPd2dQUHdEc3M2WWtGenRrWWttLTJERzVYMWJrQTZGcVh6OXlSd0JFdXdib19vY0FfdXBSbFBDUUJCMFRQZUVLVXFXbFR1NU9WTjkxUm4wU2pEVkhmWDM4dkx1TUxKUQ?oc=5</t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>539e65b6f9a2efcc9136ed8f</t>
         </is>
       </c>
-      <c r="AD8" s="3" t="inlineStr">
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>40d19c23dd7f5f4ba7086abf</t>
         </is>
       </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
         <is>
           <t>ADSK</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2165,176 +2285,204 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>HUM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Humana Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>2026-08-28T11:26:24+08:00</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Humana (HUM) Faces A 27% Fair Value Gap On $541.5 Million Overbilling Settlement</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.873</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQzJYczBfdVVoYUFXM3dScjNiUjFKZDIya2xxeW04ZUZpNDNrcHBDUm5ud2pHdXBYQW93T1ZrVFFsN24xX1pLSFBhOU40RXlXOWw3aHhOUDdJRUVuR0xmZ0hKWmx5SGhtRFhqeGk0SFYzVUxwU3VkOE10ZmRJd2Vyb1pEU0VxT0piNXM4blRCdkd0b2xqYm5pNnp0LW5NcjlxYWs4VXBzV05TOHNIVFd0amV3b2wtamFxQTE0TW5kaVRJd9IBxwFBVV95cUxNMFpaRE9WRUczb1U0dERadllTT2lxcFc2YTN6X1ktSjVfeWFLdm9PYXp2WUw0R1JPRjNLWlY5dlNTMUJxLVM0c28taTVQQjBsSVhzUFNQVEpZT1RBV21LVXA5RFRoVTJjTDMtT19HbDhNQmtjUGZyS0xMUlphRUhrMm1FMUZiMnFhcy0xSXQzazFDc2NXVmR3TTNXTzh2elhzRlRiVWZHWnotNW4tZ1dsNUZlaXBHSi1PLTd4OEVNOUxGYndMYWU4?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>8879f8f9b1bd40038a4822bbca1631cd</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>57e0ed492648aa0f69591094</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>4c7314caf830d06a2d6db808</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>'-0.873</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQzJYczBfdVVoYUFXM3dScjNiUjFKZDIya2xxeW04ZUZpNDNrcHBDUm5ud2pHdXBYQW93T1ZrVFFsN24xX1pLSFBhOU40RXlXOWw3aHhOUDdJRUVuR0xmZ0hKWmx5SGhtRFhqeGk0SFYzVUxwU3VkOE10ZmRJd2Vyb1pEU0VxT0piNXM4blRCdkd0b2xqYm5pNnp0LW5NcjlxYWs4VXBzV05TOHNIVFd0amV3b2wtamFxQTE0TW5kaVRJd9IBxwFBVV95cUxNMFpaRE9WRUczb1U0dERadllTT2lxcFc2YTN6X1ktSjVfeWFLdm9PYXp2WUw0R1JPRjNLWlY5dlNTMUJxLVM0c28taTVQQjBsSVhzUFNQVEpZT1RBV21LVXA5RFRoVTJjTDMtT19HbDhNQmtjUGZyS0xMUlphRUhrMm1FMUZiMnFhcy0xSXQzazFDc2NXVmR3TTNXTzh2elhzRlRiVWZHWnotNW4tZ1dsNUZlaXBHSi1PLTd4OEVNOUxGYndMYWU4?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>57e0ed492648aa0f69591094</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>4c7314caf830d06a2d6db808</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
         <is>
           <t>HUM</t>
         </is>
       </c>
-      <c r="BC10" s="2" t="inlineStr">
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="2" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="2" t="inlineStr">
+      <c r="BG10" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2366,32 +2514,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2431,7 +2579,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2440,7 +2588,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>1f7fa17bb99c4aa89508560dd888571c</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>b0bafb43203fae7530132a60</t>
@@ -2463,7 +2615,7 @@
       <c r="AN11" s="2" t="inlineStr"/>
       <c r="AO11" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP11" s="2" t="inlineStr"/>
@@ -2505,6 +2657,22 @@
       </c>
       <c r="BG11" s="2" t="inlineStr"/>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2675,508 +2843,548 @@
         </is>
       </c>
       <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr"/>
+      <c r="BL12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Bank of America Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>2026-08-28T08:36:35+08:00</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Judge to consider final approval of Bank of America's $72 million settlement with Epstein accusers</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQOWV5V0VsYklTLVo0UjZGRExjNXhBd0tQTXRVSW00QnhJVmlLQlJWdENmUHBhWkJQc3pqMjItY1U4eU52clVKSS02VFpaZnBBOHZaZXF3R1JvZEZJWjREZXQ3T29DV2k4UVppSjN3bjJ1aHRMT0tUcjR0emlYNlhWSnh6SDg1QU42T1M5X1I4aS0xNWVIWEZJMU50U0ttWEdNaTgwZnJIOXE2Zm1obmFaaDB4aHVRT3NCWDRPczlOUjRLQVJEU25lbUE3N2tVVExDenhzU3pYamFpOC1xVWl6SGI3aw?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>ABC7 Bay Area</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>d64dfbc740c74153853e51db674196fa</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>36e90d082ca1e51c293bcd81</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>5d79e7490b12c1e27e991a8e</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQOWV5V0VsYklTLVo0UjZGRExjNXhBd0tQTXRVSW00QnhJVmlLQlJWdENmUHBhWkJQc3pqMjItY1U4eU52clVKSS02VFpaZnBBOHZaZXF3R1JvZEZJWjREZXQ3T29DV2k4UVppSjN3bjJ1aHRMT0tUcjR0emlYNlhWSnh6SDg1QU42T1M5X1I4aS0xNWVIWEZJMU50U0ttWEdNaTgwZnJIOXE2Zm1obmFaaDB4aHVRT3NCWDRPczlOUjRLQVJEU25lbUE3N2tVVExDenhzU3pYamFpOC1xVWl6SGI3aw?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>ABC7 Bay Area</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>36e90d082ca1e51c293bcd81</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>5d79e7490b12c1e27e991a8e</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr"/>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr"/>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr"/>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
-      <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
-      <c r="AP13" s="2" t="inlineStr"/>
-      <c r="AQ13" s="2" t="inlineStr"/>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr"/>
-      <c r="AU13" s="2" t="inlineStr"/>
-      <c r="AV13" s="2" t="inlineStr"/>
-      <c r="AW13" s="2" t="inlineStr">
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr"/>
+      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX13" s="2" t="inlineStr"/>
-      <c r="AY13" s="2" t="inlineStr"/>
-      <c r="AZ13" s="2" t="inlineStr"/>
-      <c r="BA13" s="2" t="inlineStr"/>
-      <c r="BB13" s="2" t="inlineStr">
+      <c r="AX13" s="3" t="inlineStr"/>
+      <c r="AY13" s="3" t="inlineStr"/>
+      <c r="AZ13" s="3" t="inlineStr"/>
+      <c r="BA13" s="3" t="inlineStr"/>
+      <c r="BB13" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="BC13" s="2" t="inlineStr">
+      <c r="BC13" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="2" t="inlineStr"/>
-      <c r="BE13" s="2" t="inlineStr">
+      <c r="BD13" s="3" t="inlineStr"/>
+      <c r="BE13" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF13" s="2" t="inlineStr">
+      <c r="BF13" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG13" s="2" t="inlineStr">
+      <c r="BG13" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Eversource Energy</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T08:34:56+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Eversource (ES) Stock Could Be 21% Overvalued As Dividend Growth Stays Modest</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0.484</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPSVFSanBxaHNzMThjbEc3REhqdTNfWmR2dDhZcWZ0V0pZa1lvNVBzTlJ5cU4yLW9oZ1BBWUxGR0k2VE9aUXdXNmpVN0VKbE5NdHMteEVHRzQ3QnJhRk5ITnF6SGhIeTdRRXFsMHFHMHlPVmlmWVhpSXo3V0ZLMlFkbmFweFQtU1VnVXJsN2NIcEpxYkRqbVdWaWMyWDhDVmd0QnVvdGhxRUZuOVlIQmg1M0RQcHEtTzJOcFlKTmtKcGxBLXltNl9XZ1J1Qmo3UdIB0wFBVV95cUxOTEVGdTNtV29TQ3hOYWUxQmFRMk5LT2hPMFNTZWtfTWxPZ1MybmVQNEY1MEdHdWFRREJmcTlRcC1QT3M4NUVlRzNtMzdETkJKT2s2V0hZS2hCR2R4WWl4bDdBX2FZOHpOZHZmU3dyRExta01FQkxwdGhkeTlacUJzV01mNXNQQkFPcTV1ZFdjYWRpWmFVVGk1MzhZVE5IYVQ1TGk3YURZZ3E4VFpNMDNsRDlVRUtSXy1qRk1LVnRaQmQzRU04cXVMMFg5Z1dGZFFCR3RB?oc=5</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>simplywall.st</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>2424b34306368eb06f679e95</t>
         </is>
       </c>
-      <c r="AD14" s="3" t="inlineStr">
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>23073c0bf0ba907cd60be7d9</t>
         </is>
       </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr"/>
+      <c r="BG14" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>HUBB</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Hubbell Inc Common Stock</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T08:14:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Hubbell (HUBB) Stock Looks Overvalued On Cash Flow But Fair On Earnings</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>估值疑慮</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0.845</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTDJNVFU3QklnSUJNLUw3RzBrWU5sOTBLOV9saU1HdU14cDdieGw0SkNuaVk0MXFIMVdTMW8xN0NqYlRidzhfOW9xQklaeXpBTnZhRGhwSkJrNzIxb2VhTnlZdDhXbTFTeWMzbVNBdGZ3R19xeVNFb2NQOXVCZ2Y5V2szTm01LXJvb3hTb1MzMm9oUWJlM0FZUWI0SDIyTDJ6M1E?oc=5</t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>VALUATION_CONCERN</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>overvalued</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>8bc109c1134c436c0d9d07af</t>
         </is>
       </c>
-      <c r="AD15" s="3" t="inlineStr">
+      <c r="AD15" s="2" t="inlineStr">
         <is>
           <t>7c1540f0ea2d4a7cd40b4ec8</t>
         </is>
       </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr">
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>HUBB</t>
         </is>
       </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="3" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="3" t="inlineStr">
+      <c r="BG15" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3347,1357 +3555,1457 @@
         </is>
       </c>
       <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BI16" s="4" t="inlineStr"/>
+      <c r="BJ16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr"/>
+      <c r="BL16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Robinhood Markets</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T07:37:55+08:00</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Mt. Hood National Forest expands closures as wildfires burn - Oregon Public Broadcasting</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>'-0.535</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5GQ3dOd0lVeWE4YmtlNUpBdXhaN0ZOUmhfSXRtX3Rad3lfWXdqcE5YdElyV2s5Nm1MNVVOX241NFl2cVJiMWV1Y2J3TFM1RWxReE9oc1M0VUoyUE43UWg2Qy1XX0M0eUE4NUpqSDJPRzVRN1hBbW9TNkhRV2lXdw?oc=5</t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Oregon Public Broadcasting - OPB</t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>wildfire</t>
         </is>
       </c>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>e6010eef57b51356f9c95e66</t>
         </is>
       </c>
-      <c r="AD17" s="3" t="inlineStr">
+      <c r="AD17" s="2" t="inlineStr">
         <is>
           <t>b975509b6161afbd04e87c97</t>
         </is>
       </c>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr">
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr"/>
+      <c r="AL17" s="2" t="inlineStr"/>
+      <c r="AM17" s="2" t="inlineStr"/>
+      <c r="AN17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr"/>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr">
+      <c r="AP17" s="2" t="inlineStr"/>
+      <c r="AQ17" s="2" t="inlineStr"/>
+      <c r="AR17" s="2" t="inlineStr"/>
+      <c r="AS17" s="2" t="inlineStr"/>
+      <c r="AT17" s="2" t="inlineStr"/>
+      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" s="2" t="inlineStr"/>
+      <c r="AX17" s="2" t="inlineStr"/>
+      <c r="AY17" s="2" t="inlineStr"/>
+      <c r="AZ17" s="2" t="inlineStr"/>
+      <c r="BA17" s="2" t="inlineStr"/>
+      <c r="BB17" s="2" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="BC17" s="3" t="inlineStr">
+      <c r="BC17" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD17" s="3" t="inlineStr">
+      <c r="BD17" s="2" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="BE17" s="3" t="inlineStr">
+      <c r="BE17" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF17" s="3" t="inlineStr">
+      <c r="BF17" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG17" s="3" t="inlineStr"/>
-      <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BG17" s="2" t="inlineStr"/>
+      <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>ADSK</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Autodesk, Inc.</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T05:27:05+08:00</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Autodesk預測季度利潤低於華爾街預期，股價下跌</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>https://tw.tradingview.com/symbols/NASDAQ-ADSK/news/</t>
         </is>
       </c>
-      <c r="V18" s="3" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>TradingView</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>6e1b34a863bc78854e48b08e</t>
         </is>
       </c>
-      <c r="AD18" s="3" t="inlineStr">
+      <c r="AD18" s="2" t="inlineStr">
         <is>
           <t>2ef17560faf9bf17c64c2d65</t>
         </is>
       </c>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AP18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
         <is>
           <t>ADSK</t>
         </is>
       </c>
-      <c r="BC18" s="3" t="inlineStr">
+      <c r="BC18" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH18" s="3" t="inlineStr"/>
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Marvell Technology, Inc.</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T03:55:32+08:00</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>MRVL Stock Reverses to $240 Ahead of Marvell Earnings as Chip Tariff Risks Rise</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>關稅</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>'-0.941</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPTHRFQ1JHRUxpN2s2N3NDbXNGMUgzSUFubXVicEg3ZVlpZGJMTFR3QTRHbEJuRGItSTV3RWVLQjdlN3FDZ0VIX21KcWpOWEY5Y0JNUzROZzlxaklkNnliM0hzQy1tUWo4MkZESkVfTWtidWl4OFJSZW5jNlYtMFVZd3VhUW1sRUEtc1ZnNTh5U2FQMmx0UXdEUlBrLXhrZExEZVg4cWotS19LWWxVeHVUNU1hMGpPZ3hDQjRVR3F3?oc=5</t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>FXLeaders</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>TARIFF</t>
         </is>
       </c>
-      <c r="Z19" s="3" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>b27b85e62bf984917679535b</t>
         </is>
       </c>
-      <c r="AD19" s="3" t="inlineStr">
+      <c r="AD19" s="2" t="inlineStr">
         <is>
           <t>1ed8197e7c47d001b4538746</t>
         </is>
       </c>
-      <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr"/>
-      <c r="AG19" s="3" t="inlineStr"/>
-      <c r="AH19" s="3" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
-      <c r="AM19" s="3" t="inlineStr"/>
-      <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
-      <c r="AW19" s="3" t="inlineStr">
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
+      <c r="AL19" s="2" t="inlineStr"/>
+      <c r="AM19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX19" s="3" t="inlineStr"/>
-      <c r="AY19" s="3" t="inlineStr"/>
-      <c r="AZ19" s="3" t="inlineStr"/>
-      <c r="BA19" s="3" t="inlineStr"/>
-      <c r="BB19" s="3" t="inlineStr">
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr"/>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
       </c>
-      <c r="BC19" s="3" t="inlineStr">
+      <c r="BC19" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="3" t="inlineStr"/>
-      <c r="BE19" s="3" t="inlineStr">
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF19" s="3" t="inlineStr">
+      <c r="BF19" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG19" s="3" t="inlineStr">
+      <c r="BG19" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Pentair</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>2026-08-28T03:45:22+08:00</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>PENTAIR CLASS ACTION ALERT: Bragar Eagel &amp; Squire, P.C.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxQOFZVeF9XRFNleFZJLUhSYkoxZUZISUdLUWk2NlBQdUd0V1k5V3h2TGNIREtMc3BjWG1rbnRodkc1alZRS2lUZ1M4cDlkZ2hqX0M3V3N3eTVEZjNKM2JZV1NQSDVwMU1aT3owRjFNQ0NmRWR1LWFiRGg2OE1PVVVYVm9leHJmYmtLdmNZTTR1c3R2WW9ydzFGcFBIYWcySktCdTV4LTZiV0ZqUUtfbzVwU0dVRWJhSmFyQm9VQnBubDRiRFVSd1YwOHY1UnNuOXpOcUktLS1WWE9NMXE2QWw5aWJnRDlfdzl5WWNJSEZEMmtXclNLWE0tS3diel9FQU8xakpqZHVvNmxVeW9RRWN1bVNuQ1hILXF3M0pLR0taSlVjN2NxblNDcnJFU0hqQ0tmS3hHaG9tbURhWEVqaTFZenFuSzY?oc=5</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>ed31d2e466574160a597ad9bf2d66732</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>6620fc0f873a145ca08568af</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>becd80dd500a64133a6ce5b3</t>
+        </is>
+      </c>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxQOFZVeF9XRFNleFZJLUhSYkoxZUZISUdLUWk2NlBQdUd0V1k5V3h2TGNIREtMc3BjWG1rbnRodkc1alZRS2lUZ1M4cDlkZ2hqX0M3V3N3eTVEZjNKM2JZV1NQSDVwMU1aT3owRjFNQ0NmRWR1LWFiRGg2OE1PVVVYVm9leHJmYmtLdmNZTTR1c3R2WW9ydzFGcFBIYWcySktCdTV4LTZiV0ZqUUtfbzVwU0dVRWJhSmFyQm9VQnBubDRiRFVSd1YwOHY1UnNuOXpOcUktLS1WWE9NMXE2QWw5aWJnRDlfdzl5WWNJSEZEMmtXclNLWE0tS3diel9FQU8xakpqZHVvNmxVeW9RRWN1bVNuQ1hILXF3M0pLR0taSlVjN2NxblNDcnJFU0hqQ0tmS3hHaG9tbURhWEVqaTFZenFuSzY?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr"/>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>6620fc0f873a145ca08568af</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="inlineStr">
-        <is>
-          <t>becd80dd500a64133a6ce5b3</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="inlineStr"/>
-      <c r="AF20" s="2" t="inlineStr"/>
-      <c r="AG20" s="2" t="inlineStr"/>
-      <c r="AH20" s="2" t="inlineStr"/>
-      <c r="AI20" s="2" t="inlineStr"/>
-      <c r="AJ20" s="2" t="inlineStr"/>
-      <c r="AK20" s="2" t="inlineStr"/>
-      <c r="AL20" s="2" t="inlineStr"/>
-      <c r="AM20" s="2" t="inlineStr"/>
-      <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
-      <c r="AP20" s="2" t="inlineStr"/>
-      <c r="AQ20" s="2" t="inlineStr"/>
-      <c r="AR20" s="2" t="inlineStr"/>
-      <c r="AS20" s="2" t="inlineStr"/>
-      <c r="AT20" s="2" t="inlineStr"/>
-      <c r="AU20" s="2" t="inlineStr"/>
-      <c r="AV20" s="2" t="inlineStr"/>
-      <c r="AW20" s="2" t="inlineStr"/>
-      <c r="AX20" s="2" t="inlineStr"/>
-      <c r="AY20" s="2" t="inlineStr"/>
-      <c r="AZ20" s="2" t="inlineStr"/>
-      <c r="BA20" s="2" t="inlineStr"/>
-      <c r="BB20" s="2" t="inlineStr">
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr"/>
+      <c r="AS20" s="3" t="inlineStr"/>
+      <c r="AT20" s="3" t="inlineStr"/>
+      <c r="AU20" s="3" t="inlineStr"/>
+      <c r="AV20" s="3" t="inlineStr"/>
+      <c r="AW20" s="3" t="inlineStr"/>
+      <c r="AX20" s="3" t="inlineStr"/>
+      <c r="AY20" s="3" t="inlineStr"/>
+      <c r="AZ20" s="3" t="inlineStr"/>
+      <c r="BA20" s="3" t="inlineStr"/>
+      <c r="BB20" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="BC20" s="2" t="inlineStr">
+      <c r="BC20" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="2" t="inlineStr"/>
-      <c r="BE20" s="2" t="inlineStr">
+      <c r="BD20" s="3" t="inlineStr"/>
+      <c r="BE20" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF20" s="2" t="inlineStr"/>
-      <c r="BG20" s="2" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr"/>
+      <c r="BG20" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>GDDY</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>GoDaddy Inc. Class A Common Stock</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>2026-08-28T03:07:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>SueWallSt Reminds GoDaddy Inc. Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 20, 2026 - GDDY</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>'-0.072</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOWFNsdUU2TVVXU2t6djFQQlpqMFpfcWtXWnJHZ3NERzFGa0xzUWFEdlIybnpZNzFnVl9TOWxMa2M4N19GYXl0cW5GZU5nR25hZklFc09nUGtKY2FZSERlUEZyTDAtTHhOa1lBWjJITUl2ejhtTWc1MUxMZFpIMWx0WEp2T2d0VlktNnd0NVZpeE9kaUJ2NXVRNG9UQThRaVNGcDZVSVJOZ2c3ZEhGSjRyZDRhSVc2b01hN2RPeGRYZ3Y0U2d5QnRKWTlpdG5EWWtXNkkzTHR4Sk1OeU4yam1QSk1hZ3l1MjM1aVo4dzczVU91SC1xWnExdnBwOE5qYndjVzByTGRxN0VxZ3ZIUXJoazRVT2E0cWpVYW5Z?oc=5</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>fabca78aca8a431d83e275b9fc14d273</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>a49c911a8ad6f60543b8b451</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>3245a856ccbcb227925ccec7</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>'-0.072</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOWFNsdUU2TVVXU2t6djFQQlpqMFpfcWtXWnJHZ3NERzFGa0xzUWFEdlIybnpZNzFnVl9TOWxMa2M4N19GYXl0cW5GZU5nR25hZklFc09nUGtKY2FZSERlUEZyTDAtTHhOa1lBWjJITUl2ejhtTWc1MUxMZFpIMWx0WEp2T2d0VlktNnd0NVZpeE9kaUJ2NXVRNG9UQThRaVNGcDZVSVJOZ2c3ZEhGSjRyZDRhSVc2b01hN2RPeGRYZ3Y0U2d5QnRKWTlpdG5EWWtXNkkzTHR4Sk1OeU4yam1QSk1hZ3l1MjM1aVo4dzczVU91SC1xWnExdnBwOE5qYndjVzByTGRxN0VxZ3ZIUXJoazRVT2E0cWpVYW5Z?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr"/>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>a49c911a8ad6f60543b8b451</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>3245a856ccbcb227925ccec7</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr"/>
-      <c r="AF21" s="2" t="inlineStr"/>
-      <c r="AG21" s="2" t="inlineStr"/>
-      <c r="AH21" s="2" t="inlineStr"/>
-      <c r="AI21" s="2" t="inlineStr"/>
-      <c r="AJ21" s="2" t="inlineStr"/>
-      <c r="AK21" s="2" t="inlineStr"/>
-      <c r="AL21" s="2" t="inlineStr"/>
-      <c r="AM21" s="2" t="inlineStr"/>
-      <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
-      <c r="AP21" s="2" t="inlineStr"/>
-      <c r="AQ21" s="2" t="inlineStr"/>
-      <c r="AR21" s="2" t="inlineStr"/>
-      <c r="AS21" s="2" t="inlineStr"/>
-      <c r="AT21" s="2" t="inlineStr"/>
-      <c r="AU21" s="2" t="inlineStr"/>
-      <c r="AV21" s="2" t="inlineStr"/>
-      <c r="AW21" s="2" t="inlineStr">
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr"/>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX21" s="2" t="inlineStr"/>
-      <c r="AY21" s="2" t="inlineStr"/>
-      <c r="AZ21" s="2" t="inlineStr"/>
-      <c r="BA21" s="2" t="inlineStr"/>
-      <c r="BB21" s="2" t="inlineStr">
+      <c r="AX21" s="3" t="inlineStr"/>
+      <c r="AY21" s="3" t="inlineStr"/>
+      <c r="AZ21" s="3" t="inlineStr"/>
+      <c r="BA21" s="3" t="inlineStr"/>
+      <c r="BB21" s="3" t="inlineStr">
         <is>
           <t>GDDY</t>
         </is>
       </c>
-      <c r="BC21" s="2" t="inlineStr">
+      <c r="BC21" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="2" t="inlineStr"/>
-      <c r="BE21" s="2" t="inlineStr">
+      <c r="BD21" s="3" t="inlineStr"/>
+      <c r="BE21" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF21" s="2" t="inlineStr">
+      <c r="BF21" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG21" s="2" t="inlineStr">
+      <c r="BG21" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Ameriprise Financial, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T02:47:34+08:00</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ameriprise Financial: Improving Macro Justifies The Rally (Downgrade) (NYSE:AMP)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0.227</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPVzY4V2xkdjJLenhMeWlHamRvUTJDLW5WcTRycmRaRVJGMmF2cW15cnI0ZEt4X2wzQXVPWUNXNDZEd3FubnVpNnJLck92ZFEwSjNIZVpfdTVrajNIbjlKV1B3MHpPTWFwbGEwWkdaTWdfWU9Mbkh5SlpSeHpyOWh4eWhwR3NyMEpxR0wzV3hOMzlVMWhrdnR1SDhCam1kX24ycjhXX3BtZm1VcXM?oc=5</t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z22" s="3" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>017a9cfcce3c6f153b2ec826</t>
         </is>
       </c>
-      <c r="AD22" s="3" t="inlineStr">
+      <c r="AD22" s="2" t="inlineStr">
         <is>
           <t>540d6872baf6b6a0e07e416f</t>
         </is>
       </c>
-      <c r="AE22" s="3" t="inlineStr"/>
-      <c r="AF22" s="3" t="inlineStr"/>
-      <c r="AG22" s="3" t="inlineStr"/>
-      <c r="AH22" s="3" t="inlineStr"/>
-      <c r="AI22" s="3" t="inlineStr"/>
-      <c r="AJ22" s="3" t="inlineStr"/>
-      <c r="AK22" s="3" t="inlineStr"/>
-      <c r="AL22" s="3" t="inlineStr"/>
-      <c r="AM22" s="3" t="inlineStr"/>
-      <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
-      <c r="AP22" s="3" t="inlineStr"/>
-      <c r="AQ22" s="3" t="inlineStr"/>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr"/>
-      <c r="AV22" s="3" t="inlineStr"/>
-      <c r="AW22" s="3" t="inlineStr">
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr"/>
+      <c r="AL22" s="2" t="inlineStr"/>
+      <c r="AM22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AP22" s="2" t="inlineStr"/>
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="inlineStr"/>
+      <c r="AS22" s="2" t="inlineStr"/>
+      <c r="AT22" s="2" t="inlineStr"/>
+      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX22" s="3" t="inlineStr"/>
-      <c r="AY22" s="3" t="inlineStr"/>
-      <c r="AZ22" s="3" t="inlineStr"/>
-      <c r="BA22" s="3" t="inlineStr"/>
-      <c r="BB22" s="3" t="inlineStr">
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr"/>
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
-      <c r="BC22" s="3" t="inlineStr">
+      <c r="BC22" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD22" s="3" t="inlineStr"/>
-      <c r="BE22" s="3" t="inlineStr">
+      <c r="BD22" s="2" t="inlineStr"/>
+      <c r="BE22" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BG22" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr"/>
+      <c r="BL22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T01:50:31+08:00</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>World in Brief: Nvidia’s record earnings; catastrophic floods sweep Nepal</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNFZHWnFadzdENE8xdDI1Q040SW9oSjZVSTE4TDBsVUsxMmdiQklEdVl1WjNMbEhPRVJTSk1qZmJMRDdSeHFZRjY2OV8tRmZDSXdLUEh3UDNvcWdLQWYzUjMtMFlYd0Fnbi0tbDBRR3Zta0VXb29FWHNFbDdxNlI0Q0VKTHZGUDgtYk41Y3B2VEQtWnhLQXUw?oc=5</t>
         </is>
       </c>
-      <c r="V23" s="3" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>The Economist</t>
         </is>
       </c>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z23" s="3" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>flood</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="inlineStr"/>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>5991a77c93e8edc6aab8c90f</t>
         </is>
       </c>
-      <c r="AD23" s="3" t="inlineStr">
+      <c r="AD23" s="2" t="inlineStr">
         <is>
           <t>bbcdf6f73145c9254fdf6d98</t>
         </is>
       </c>
-      <c r="AE23" s="3" t="inlineStr"/>
-      <c r="AF23" s="3" t="inlineStr"/>
-      <c r="AG23" s="3" t="inlineStr"/>
-      <c r="AH23" s="3" t="inlineStr"/>
-      <c r="AI23" s="3" t="inlineStr"/>
-      <c r="AJ23" s="3" t="inlineStr"/>
-      <c r="AK23" s="3" t="inlineStr"/>
-      <c r="AL23" s="3" t="inlineStr"/>
-      <c r="AM23" s="3" t="inlineStr"/>
-      <c r="AN23" s="3" t="inlineStr"/>
-      <c r="AO23" s="3" t="inlineStr"/>
-      <c r="AP23" s="3" t="inlineStr"/>
-      <c r="AQ23" s="3" t="inlineStr"/>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr"/>
-      <c r="AV23" s="3" t="inlineStr"/>
-      <c r="AW23" s="3" t="inlineStr">
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+      <c r="AK23" s="2" t="inlineStr"/>
+      <c r="AL23" s="2" t="inlineStr"/>
+      <c r="AM23" s="2" t="inlineStr"/>
+      <c r="AN23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AP23" s="2" t="inlineStr"/>
+      <c r="AQ23" s="2" t="inlineStr"/>
+      <c r="AR23" s="2" t="inlineStr"/>
+      <c r="AS23" s="2" t="inlineStr"/>
+      <c r="AT23" s="2" t="inlineStr"/>
+      <c r="AU23" s="2" t="inlineStr"/>
+      <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX23" s="3" t="inlineStr"/>
-      <c r="AY23" s="3" t="inlineStr"/>
-      <c r="AZ23" s="3" t="inlineStr"/>
-      <c r="BA23" s="3" t="inlineStr"/>
-      <c r="BB23" s="3" t="inlineStr">
+      <c r="AX23" s="2" t="inlineStr"/>
+      <c r="AY23" s="2" t="inlineStr"/>
+      <c r="AZ23" s="2" t="inlineStr"/>
+      <c r="BA23" s="2" t="inlineStr"/>
+      <c r="BB23" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC23" s="3" t="inlineStr">
+      <c r="BC23" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD23" s="3" t="inlineStr"/>
-      <c r="BE23" s="3" t="inlineStr">
+      <c r="BD23" s="2" t="inlineStr"/>
+      <c r="BE23" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF23" s="3" t="inlineStr">
+      <c r="BF23" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG23" s="3" t="inlineStr">
+      <c r="BG23" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH23" s="3" t="inlineStr"/>
+      <c r="BH23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr"/>
+      <c r="BL23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Bank of America Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>2026-08-28T01:25:25+08:00</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Court approves Bank of America’s $72.5M settlement with Epstein accusers</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNHVyYkxUNjJhTDVwWVJ6ZUdZTjUzazFLdndxVlBJVVgzMXQtNWZFbHdpM2taYnJ3UFFJbWVucnBtQUM1bXVlNFNTRzlIczJfTFYwVm5GX2lmMnJlc05BNDA2QUVLRkp3ZUpTSW1kYUY5UlgwQ3BCaVhUaEdJRGpoeGktel8wNE1tbGNqZFp6NGpaWTdfOXF5T0RwQ2ZzUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>Maryland Daily Record</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>8a938431d8f34286865149e1237129a0</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>f93b7abdfabcf569fd2cd94b</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>bab403c9efc026019d7c4cb0</t>
+        </is>
+      </c>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNHVyYkxUNjJhTDVwWVJ6ZUdZTjUzazFLdndxVlBJVVgzMXQtNWZFbHdpM2taYnJ3UFFJbWVucnBtQUM1bXVlNFNTRzlIczJfTFYwVm5GX2lmMnJlc05BNDA2QUVLRkp3ZUpTSW1kYUY5UlgwQ3BCaVhUaEdJRGpoeGktel8wNE1tbGNqZFp6NGpaWTdfOXF5T0RwQ2ZzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Maryland Daily Record</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr"/>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>f93b7abdfabcf569fd2cd94b</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="inlineStr">
-        <is>
-          <t>bab403c9efc026019d7c4cb0</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="inlineStr"/>
-      <c r="AF24" s="2" t="inlineStr"/>
-      <c r="AG24" s="2" t="inlineStr"/>
-      <c r="AH24" s="2" t="inlineStr"/>
-      <c r="AI24" s="2" t="inlineStr"/>
-      <c r="AJ24" s="2" t="inlineStr"/>
-      <c r="AK24" s="2" t="inlineStr"/>
-      <c r="AL24" s="2" t="inlineStr"/>
-      <c r="AM24" s="2" t="inlineStr"/>
-      <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
-      <c r="AP24" s="2" t="inlineStr"/>
-      <c r="AQ24" s="2" t="inlineStr"/>
-      <c r="AR24" s="2" t="inlineStr"/>
-      <c r="AS24" s="2" t="inlineStr"/>
-      <c r="AT24" s="2" t="inlineStr"/>
-      <c r="AU24" s="2" t="inlineStr"/>
-      <c r="AV24" s="2" t="inlineStr"/>
-      <c r="AW24" s="2" t="inlineStr">
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr"/>
+      <c r="AS24" s="3" t="inlineStr"/>
+      <c r="AT24" s="3" t="inlineStr"/>
+      <c r="AU24" s="3" t="inlineStr"/>
+      <c r="AV24" s="3" t="inlineStr"/>
+      <c r="AW24" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX24" s="2" t="inlineStr"/>
-      <c r="AY24" s="2" t="inlineStr"/>
-      <c r="AZ24" s="2" t="inlineStr"/>
-      <c r="BA24" s="2" t="inlineStr"/>
-      <c r="BB24" s="2" t="inlineStr">
+      <c r="AX24" s="3" t="inlineStr"/>
+      <c r="AY24" s="3" t="inlineStr"/>
+      <c r="AZ24" s="3" t="inlineStr"/>
+      <c r="BA24" s="3" t="inlineStr"/>
+      <c r="BB24" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="BC24" s="2" t="inlineStr">
+      <c r="BC24" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD24" s="2" t="inlineStr"/>
-      <c r="BE24" s="2" t="inlineStr">
+      <c r="BD24" s="3" t="inlineStr"/>
+      <c r="BE24" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF24" s="2" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG24" s="2" t="inlineStr">
+      <c r="BG24" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH24" s="2" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr"/>
+      <c r="BI24" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ24" s="3" t="inlineStr"/>
+      <c r="BK24" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH24"/>
+  <autoFilter ref="A1:BL24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4708,7 +5016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4771,6 +5079,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5074,670 +5386,762 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Kroger</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T23:56:14+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Kroger to Pay $17M to Settle Class Action Over Drug Prices</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T22:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>City of Carson reaches $370M settlement with Marathon Petroleum</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>0.301</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNclNwYXl4c3VkNkhYQl84U2xGdUJabjVwRDlfOFpFQkhWN2lUSEIzTVhFdHR6LWtrTWhlNi1zQ3ZlaVVTc3pCUW9rLVdZdWdJaUJEcGtZTW1iLVE0ZVM5T0VoZnFaNmdBcnFwenNscnNzMzFEaXVZM0tNb0NBbFVYUUlYY2I4a2NpV0Ntb212UnFnSG5QLUtKYw?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Spectrum News</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>6e0f237ed05e49f7865b0256850bb1ce</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>5978c63699fa1e8a80ba9dfa</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>33d08b065a42e209c66e2bae</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.781</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZkRES1h1bGJFM0N3UWdkblhRdEw2bm5qM1o4RWo0aWNiX2NwNnd3dUpUTFk5M0dKOFBDSk0taW1iRnhJVm9CckdvNkdvN2c1MjRLNUdTRXluZjhCcjZERXB4bEJfN1pCZkRWMFB2UWRzY25SbzY3UXRFOEI3ZVhFaFE3T1pNSzVU?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Progressive Grocer</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>68ad01e8a08fd53f75f1b48d</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>4c5cfe5dcb4c1082e86ed71c</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T22:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>City of Carson reaches $370M settlement with Marathon Petroleum</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T20:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Tech layoffs tracker 2026: All the job losses across TikTok, Apple, Meta, Microsoft, Oracle and others</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.301</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.959</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNclNwYXl4c3VkNkhYQl84U2xGdUJabjVwRDlfOFpFQkhWN2lUSEIzTVhFdHR6LWtrTWhlNi1zQ3ZlaVVTc3pCUW9rLVdZdWdJaUJEcGtZTW1iLVE0ZVM5T0VoZnFaNmdBcnFwenNscnNzMzFEaXVZM0tNb0NBbFVYUUlYY2I4a2NpV0Ntb212UnFnSG5QLUtKYw?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Spectrum News</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>5978c63699fa1e8a80ba9dfa</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>33d08b065a42e209c66e2bae</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPbXlST2RyYmpKR09DQURMSGpqd0dpME9zRW9LTnJuaEJYenZrd2t3ek9MOHgtY1RuV0p1cWdsX1FPV0trWFNWczlNVUVtSmdINXdybVlyeS00alFLXy1RR0llNl9IYW9Ta21BbVZxcGVBLVA3ZVJSNF9kSUU1UjFIRDNxOUNjVXprQTlGRXZyUzVldWFwdlZDamlTNkJwdHByYTZQdnFQZlphZmxzanlXSFhSLXZSZU1lRWNVbVg4UDEwTTVHRTBueEN3MUZTdkhWamQ0VElhc1JJeF9yZ2ZlLVlKajRDZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Tech</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>28cd053747b867acc93804fe</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>fc4db311719d37bb8005ad41</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG3" s="4" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr"/>
+      <c r="BL3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>TSCO</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Tractor Supply</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T21:23:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tractor Supply Can’t Escape Employee Tobacco Penalty Lawsuit</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>HRL</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Hormel Foods Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T16:22:01+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>HRL Q2 Deep Dive: Volumes Decline, Margin Pressures Persist, Management Eyes Brand Investment</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.545</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.948</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSHJGbnhnSUNoN2h2OWJyXzU0TUctbkVLT2VYTGdqUHdUbDFSeTQtNDFsVVltNi1SSV93cE9oZEdJbUc5NTc1VDFVTjJMVi0zTEg2ZnpLQzZYd2dZQUw5Z0s4M1dSRWVNbF9nSXN4R2l2RFNPSkVwRVhmdXpvWHBqb2w4S2ptQXRYQl9lMElCeTNFVUlYVUlaUk9IUW1EMko1dzNWRk5JNVdNcERFTUNR?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>news.bloombergtax.com</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>11429a7f0a6964d43a66935e</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>5d6f5e5e5ad9f3412d980c87</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>TSCO</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOODFQQi1jNjVPVGp2d3hTYzBBcnpQTGg0eVhFUlBOOUZBVGQ4c01aaEhyQjlGUy1BLWoxbjZRX0dYa3FBLXFpMHNua1ppdHU1SHFfTEJvNXpoR0FQZU9NMG9jZVVXZ0hLQS1FY182TDRmemMydEtFUXk4elZ5cllWTmxacWZ6OFVBU2dPV0o5ckllVUU?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>bf7c7ad3b95b58efe84c4198</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>d83699b13932c7eb7a3bb9a5</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>HRL</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr"/>
-      <c r="BG4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-28T20:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Tech layoffs tracker 2026: All the job losses across TikTok, Apple, Meta, Microsoft, Oracle and others</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>HUM</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Humana Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T11:26:24+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Humana (HUM) Faces A 27% Fair Value Gap On $541.5 Million Overbilling Settlement</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>'-0.873</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQzJYczBfdVVoYUFXM3dScjNiUjFKZDIya2xxeW04ZUZpNDNrcHBDUm5ud2pHdXBYQW93T1ZrVFFsN24xX1pLSFBhOU40RXlXOWw3aHhOUDdJRUVuR0xmZ0hKWmx5SGhtRFhqeGk0SFYzVUxwU3VkOE10ZmRJd2Vyb1pEU0VxT0piNXM4blRCdkd0b2xqYm5pNnp0LW5NcjlxYWs4VXBzV05TOHNIVFd0amV3b2wtamFxQTE0TW5kaVRJd9IBxwFBVV95cUxNMFpaRE9WRUczb1U0dERadllTT2lxcFc2YTN6X1ktSjVfeWFLdm9PYXp2WUw0R1JPRjNLWlY5dlNTMUJxLVM0c28taTVQQjBsSVhzUFNQVEpZT1RBV21LVXA5RFRoVTJjTDMtT19HbDhNQmtjUGZyS0xMUlphRUhrMm1FMUZiMnFhcy0xSXQzazFDc2NXVmR3TTNXTzh2elhzRlRiVWZHWnotNW4tZ1dsNUZlaXBHSi1PLTd4OEVNOUxGYndMYWU4?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>8879f8f9b1bd40038a4822bbca1631cd</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>57e0ed492648aa0f69591094</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>4c7314caf830d06a2d6db808</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>'-0.959</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPbXlST2RyYmpKR09DQURMSGpqd0dpME9zRW9LTnJuaEJYenZrd2t3ek9MOHgtY1RuV0p1cWdsX1FPV0trWFNWczlNVUVtSmdINXdybVlyeS00alFLXy1RR0llNl9IYW9Ta21BbVZxcGVBLVA3ZVJSNF9kSUU1UjFIRDNxOUNjVXprQTlGRXZyUzVldWFwdlZDamlTNkJwdHByYTZQdnFQZlphZmxzanlXSFhSLXZSZU1lRWNVbVg4UDEwTTVHRTBueEN3MUZTdkhWamQ0VElhc1JJeF9yZ2ZlLVlKajRDZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Tech</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>28cd053747b867acc93804fe</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>fc4db311719d37bb8005ad41</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>HUM</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -5752,22 +6156,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Hormel Foods Corporation Common Stock</t>
+          <t>HP Inc. Common Stock</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T16:22:01+08:00</t>
+          <t>2026-08-28T09:53:00+08:00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>HRL Q2 Deep Dive: Volumes Decline, Margin Pressures Persist, Management Eyes Brand Investment</t>
+          <t>HPQ Q2 Deep Dive: AI PCs Drive Growth Amid Margin Pressures and Cautious Outlook</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -5804,7 +6208,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>'-0.948</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -5813,12 +6217,12 @@
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>原始代號與公司名稱交叉核對</t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOODFQQi1jNjVPVGp2d3hTYzBBcnpQTGg0eVhFUlBOOUZBVGQ4c01aaEhyQjlGUy1BLWoxbjZRX0dYa3FBLXFpMHNua1ppdHU1SHFfTEJvNXpoR0FQZU9NMG9jZVVXZ0hLQS1FY182TDRmemMydEtFUXk4elZ5cllWTmxacWZ6OFVBU2dPV0o5ckllVUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcGw2YkZuTk9leEZSZXdhRVNRdFdBNjFBQXpnVFNzcVp5Qk9pNzUxdzFvR3dpMldJbEdRNTRLRllfaTJ4ejY0QmdUM213WkVyanMtZ0xXR0hRV0hmRlI1Q0EweUdBY0hrcm1hcTZPX1ZKd09NZnlQQndobkFvcS1aNHRFLWhmQjd5Yk5tZw?oc=5</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
@@ -5846,12 +6250,12 @@
       <c r="AB6" s="4" t="inlineStr"/>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>bf7c7ad3b95b58efe84c4198</t>
+          <t>8e75ff9786121fe28966481d</t>
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>d83699b13932c7eb7a3bb9a5</t>
+          <t>a44ba651f906be9b1d3a4bc9</t>
         </is>
       </c>
       <c r="AE6" s="4" t="inlineStr"/>
@@ -5883,7 +6287,7 @@
       <c r="BA6" s="4" t="inlineStr"/>
       <c r="BB6" s="4" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
@@ -5908,1361 +6312,963 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>HUM</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Humana Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T11:26:24+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Humana (HUM) Faces A 27% Fair Value Gap On $541.5 Million Overbilling Settlement</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T08:36:35+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Judge to consider final approval of Bank of America's $72 million settlement with Epstein accusers</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQOWV5V0VsYklTLVo0UjZGRExjNXhBd0tQTXRVSW00QnhJVmlLQlJWdENmUHBhWkJQc3pqMjItY1U4eU52clVKSS02VFpaZnBBOHZaZXF3R1JvZEZJWjREZXQ3T29DV2k4UVppSjN3bjJ1aHRMT0tUcjR0emlYNlhWSnh6SDg1QU42T1M5X1I4aS0xNWVIWEZJMU50U0ttWEdNaTgwZnJIOXE2Zm1obmFaaDB4aHVRT3NCWDRPczlOUjRLQVJEU25lbUE3N2tVVExDenhzU3pYamFpOC1xVWl6SGI3aw?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>ABC7 Bay Area</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>d64dfbc740c74153853e51db674196fa</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>36e90d082ca1e51c293bcd81</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>5d79e7490b12c1e27e991a8e</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>'-0.873</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQzJYczBfdVVoYUFXM3dScjNiUjFKZDIya2xxeW04ZUZpNDNrcHBDUm5ud2pHdXBYQW93T1ZrVFFsN24xX1pLSFBhOU40RXlXOWw3aHhOUDdJRUVuR0xmZ0hKWmx5SGhtRFhqeGk0SFYzVUxwU3VkOE10ZmRJd2Vyb1pEU0VxT0piNXM4blRCdkd0b2xqYm5pNnp0LW5NcjlxYWs4VXBzV05TOHNIVFd0amV3b2wtamFxQTE0TW5kaVRJd9IBxwFBVV95cUxNMFpaRE9WRUczb1U0dERadllTT2lxcFc2YTN6X1ktSjVfeWFLdm9PYXp2WUw0R1JPRjNLWlY5dlNTMUJxLVM0c28taTVQQjBsSVhzUFNQVEpZT1RBV21LVXA5RFRoVTJjTDMtT19HbDhNQmtjUGZyS0xMUlphRUhrMm1FMUZiMnFhcy0xSXQzazFDc2NXVmR3TTNXTzh2elhzRlRiVWZHWnotNW4tZ1dsNUZlaXBHSi1PLTd4OEVNOUxGYndMYWU4?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>57e0ed492648aa0f69591094</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>4c7314caf830d06a2d6db808</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr"/>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr">
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="2" t="inlineStr"/>
-      <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr"/>
-      <c r="BA7" s="2" t="inlineStr"/>
-      <c r="BB7" s="2" t="inlineStr">
-        <is>
-          <t>HUM</t>
-        </is>
-      </c>
-      <c r="BC7" s="2" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="2" t="inlineStr"/>
-      <c r="BE7" s="2" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="2" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="2" t="inlineStr">
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T10:27:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Last minute penalty lifts Arkansas State women’s soccer past Stephen F. Austin</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Starbucks Corporation</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T08:10:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Starbucks (SBUX)’s Corporate Layoffs Could Strengthen its Turnaround, But Risks Remain</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>'-0.059</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRjk0ZUY1N1hGdU9XekZZNFVNLUtkZkNEdVpNZmZ4NF9tOFRWa29XeUw3TVNHdXpNTlc3dnJ2dk0wNGVkNi1FV3JTSzNLRzROLWFETjdhS2hQZTQzOEdxazVDd002Q01TWWczckFKdnpSaWZpRDJ4RjZlbFZDYVZMQ055ZmxGYkNpQ0hJTWpzdHZFSWJMTXpYR18zTXdzOEJ5Zktodjlsb2VnVzJPTVFJ0gHDAUFVX3lxTE55S0FtNkQxd3VieWVmUy1SemlTVXhEdE1nREZJUXlZUGZVYUtVcGZJWEk5VnV4a1Q0dmlPSzBFZDFzQXd3eEdHZXZKT1lTaS00RVE0VTl0cUdLc2I1TDIyUTVYRV93Zk1DQWNEQmJTT1ZCNVVkdFQ1ZjZhNk0xT3gxa1U0eUpvdUNmcmlocUNsWURyOUtKRTVib01VNk1jcDJHZU5MSUU5UC1qaWpwRGxoSElUeEU2NTdnc2pXNjdUZnBfSQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>K8 News | Jonesboro, Arkansas</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>b0bafb43203fae7530132a60</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>44d610cecd4564b7ccd32929</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="inlineStr"/>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr"/>
-      <c r="AW8" s="2" t="inlineStr"/>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr"/>
-      <c r="AZ8" s="2" t="inlineStr"/>
-      <c r="BA8" s="2" t="inlineStr"/>
-      <c r="BB8" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="BC8" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="BE8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="2" t="inlineStr"/>
-      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>'-0.686</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOUlFUQUtYdG9KYzlfVTFXeHpsY2wwZzRHendmbEJkX2JxOGx3YTJXWlc4d1hTcTdRelRHOFRmMDVsdWpQTjZVODdxU0ticlE1YzFqSW5wTjhOR0xlT2RQSVVRNmN1RFVGTThTU1hSdEZVQi0tYS1ZdVNMSW9TanRhQlpkdXpiajZmbjVYblczVUVKYnNVQ3doY1V1czlxWWs1cG5ITVlR?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>843cd612cdc5d8bcdd4f7c77</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>2e750ae64f16765acb85ca7c</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="BC8" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG8" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>HPQ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>HP Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-28T09:53:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>HPQ Q2 Deep Dive: AI PCs Drive Growth Amid Margin Pressures and Cautious Outlook</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T03:45:22+08:00</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>PENTAIR CLASS ACTION ALERT: Bragar Eagel &amp; Squire, P.C.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxQOFZVeF9XRFNleFZJLUhSYkoxZUZISUdLUWk2NlBQdUd0V1k5V3h2TGNIREtMc3BjWG1rbnRodkc1alZRS2lUZ1M4cDlkZ2hqX0M3V3N3eTVEZjNKM2JZV1NQSDVwMU1aT3owRjFNQ0NmRWR1LWFiRGg2OE1PVVVYVm9leHJmYmtLdmNZTTR1c3R2WW9ydzFGcFBIYWcySktCdTV4LTZiV0ZqUUtfbzVwU0dVRWJhSmFyQm9VQnBubDRiRFVSd1YwOHY1UnNuOXpOcUktLS1WWE9NMXE2QWw5aWJnRDlfdzl5WWNJSEZEMmtXclNLWE0tS3diel9FQU8xakpqZHVvNmxVeW9RRWN1bVNuQ1hILXF3M0pLR0taSlVjN2NxblNDcnJFU0hqQ0tmS3hHaG9tbURhWEVqaTFZenFuSzY?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>ed31d2e466574160a597ad9bf2d66732</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>6620fc0f873a145ca08568af</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>becd80dd500a64133a6ce5b3</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcGw2YkZuTk9leEZSZXdhRVNRdFdBNjFBQXpnVFNzcVp5Qk9pNzUxdzFvR3dpMldJbEdRNTRLRllfaTJ4ejY0QmdUM213WkVyanMtZ0xXR0hRV0hmRlI1Q0EweUdBY0hrcm1hcTZPX1ZKd09NZnlQQndobkFvcS1aNHRFLWhmQjd5Yk5tZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>8e75ff9786121fe28966481d</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>a44ba651f906be9b1d3a4bc9</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
-        <is>
-          <t>HPQ</t>
-        </is>
-      </c>
-      <c r="BC9" s="4" t="inlineStr">
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr"/>
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC9" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF9" s="3" t="inlineStr"/>
+      <c r="BG9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T08:36:35+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Judge to consider final approval of Bank of America's $72 million settlement with Epstein accusers</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc. Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T03:07:00+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SueWallSt Reminds GoDaddy Inc. Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 20, 2026 - GDDY</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.072</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOWFNsdUU2TVVXU2t6djFQQlpqMFpfcWtXWnJHZ3NERzFGa0xzUWFEdlIybnpZNzFnVl9TOWxMa2M4N19GYXl0cW5GZU5nR25hZklFc09nUGtKY2FZSERlUEZyTDAtTHhOa1lBWjJITUl2ejhtTWc1MUxMZFpIMWx0WEp2T2d0VlktNnd0NVZpeE9kaUJ2NXVRNG9UQThRaVNGcDZVSVJOZ2c3ZEhGSjRyZDRhSVc2b01hN2RPeGRYZ3Y0U2d5QnRKWTlpdG5EWWtXNkkzTHR4Sk1OeU4yam1QSk1hZ3l1MjM1aVo4dzczVU91SC1xWnExdnBwOE5qYndjVzByTGRxN0VxZ3ZIUXJoazRVT2E0cWpVYW5Z?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>fabca78aca8a431d83e275b9fc14d273</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>a49c911a8ad6f60543b8b451</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>3245a856ccbcb227925ccec7</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQOWV5V0VsYklTLVo0UjZGRExjNXhBd0tQTXRVSW00QnhJVmlLQlJWdENmUHBhWkJQc3pqMjItY1U4eU52clVKSS02VFpaZnBBOHZaZXF3R1JvZEZJWjREZXQ3T29DV2k4UVppSjN3bjJ1aHRMT0tUcjR0emlYNlhWSnh6SDg1QU42T1M5X1I4aS0xNWVIWEZJMU50U0ttWEdNaTgwZnJIOXE2Zm1obmFaaDB4aHVRT3NCWDRPczlOUjRLQVJEU25lbUE3N2tVVExDenhzU3pYamFpOC1xVWl6SGI3aw?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>ABC7 Bay Area</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>36e90d082ca1e51c293bcd81</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>5d79e7490b12c1e27e991a8e</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="2" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="2" t="inlineStr">
+      <c r="BG10" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Starbucks Corporation</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-28T08:10:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Starbucks (SBUX)’s Corporate Layoffs Could Strengthen its Turnaround, But Risks Remain</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T01:25:25+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Court approves Bank of America’s $72.5M settlement with Epstein accusers</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNHVyYkxUNjJhTDVwWVJ6ZUdZTjUzazFLdndxVlBJVVgzMXQtNWZFbHdpM2taYnJ3UFFJbWVucnBtQUM1bXVlNFNTRzlIczJfTFYwVm5GX2lmMnJlc05BNDA2QUVLRkp3ZUpTSW1kYUY5UlgwQ3BCaVhUaEdJRGpoeGktel8wNE1tbGNqZFp6NGpaWTdfOXF5T0RwQ2ZzUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Maryland Daily Record</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>8a938431d8f34286865149e1237129a0</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>f93b7abdfabcf569fd2cd94b</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>bab403c9efc026019d7c4cb0</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>'-0.686</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOUlFUQUtYdG9KYzlfVTFXeHpsY2wwZzRHendmbEJkX2JxOGx3YTJXWlc4d1hTcTdRelRHOFRmMDVsdWpQTjZVODdxU0ticlE1YzFqSW5wTjhOR0xlT2RQSVVRNmN1RFVGTThTU1hSdEZVQi0tYS1ZdVNMSW9TanRhQlpkdXpiajZmbjVYblczVUVKYnNVQ3doY1V1czlxWWs1cG5ITVlR?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>843cd612cdc5d8bcdd4f7c77</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>2e750ae64f16765acb85ca7c</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr"/>
+      <c r="AY11" s="3" t="inlineStr"/>
+      <c r="AZ11" s="3" t="inlineStr"/>
+      <c r="BA11" s="3" t="inlineStr"/>
+      <c r="BB11" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="BC11" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="4" t="inlineStr">
+      <c r="BD11" s="3" t="inlineStr"/>
+      <c r="BE11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T03:45:22+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>PENTAIR CLASS ACTION ALERT: Bragar Eagel &amp; Squire, P.C.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxQOFZVeF9XRFNleFZJLUhSYkoxZUZISUdLUWk2NlBQdUd0V1k5V3h2TGNIREtMc3BjWG1rbnRodkc1alZRS2lUZ1M4cDlkZ2hqX0M3V3N3eTVEZjNKM2JZV1NQSDVwMU1aT3owRjFNQ0NmRWR1LWFiRGg2OE1PVVVYVm9leHJmYmtLdmNZTTR1c3R2WW9ydzFGcFBIYWcySktCdTV4LTZiV0ZqUUtfbzVwU0dVRWJhSmFyQm9VQnBubDRiRFVSd1YwOHY1UnNuOXpOcUktLS1WWE9NMXE2QWw5aWJnRDlfdzl5WWNJSEZEMmtXclNLWE0tS3diel9FQU8xakpqZHVvNmxVeW9RRWN1bVNuQ1hILXF3M0pLR0taSlVjN2NxblNDcnJFU0hqQ0tmS3hHaG9tbURhWEVqaTFZenFuSzY?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>6620fc0f873a145ca08568af</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>becd80dd500a64133a6ce5b3</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr"/>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC12" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF12" s="2" t="inlineStr"/>
-      <c r="BG12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>GDDY</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>GoDaddy Inc. Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T03:07:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>SueWallSt Reminds GoDaddy Inc. Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 20, 2026 - GDDY</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>'-0.072</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOWFNsdUU2TVVXU2t6djFQQlpqMFpfcWtXWnJHZ3NERzFGa0xzUWFEdlIybnpZNzFnVl9TOWxMa2M4N19GYXl0cW5GZU5nR25hZklFc09nUGtKY2FZSERlUEZyTDAtTHhOa1lBWjJITUl2ejhtTWc1MUxMZFpIMWx0WEp2T2d0VlktNnd0NVZpeE9kaUJ2NXVRNG9UQThRaVNGcDZVSVJOZ2c3ZEhGSjRyZDRhSVc2b01hN2RPeGRYZ3Y0U2d5QnRKWTlpdG5EWWtXNkkzTHR4Sk1OeU4yam1QSk1hZ3l1MjM1aVo4dzczVU91SC1xWnExdnBwOE5qYndjVzByTGRxN0VxZ3ZIUXJoazRVT2E0cWpVYW5Z?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>a49c911a8ad6f60543b8b451</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>3245a856ccbcb227925ccec7</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr"/>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr"/>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr"/>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
-      <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
-      <c r="AP13" s="2" t="inlineStr"/>
-      <c r="AQ13" s="2" t="inlineStr"/>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr"/>
-      <c r="AU13" s="2" t="inlineStr"/>
-      <c r="AV13" s="2" t="inlineStr"/>
-      <c r="AW13" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX13" s="2" t="inlineStr"/>
-      <c r="AY13" s="2" t="inlineStr"/>
-      <c r="AZ13" s="2" t="inlineStr"/>
-      <c r="BA13" s="2" t="inlineStr"/>
-      <c r="BB13" s="2" t="inlineStr">
-        <is>
-          <t>GDDY</t>
-        </is>
-      </c>
-      <c r="BC13" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="2" t="inlineStr"/>
-      <c r="BE13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG13" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T01:25:25+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Court approves Bank of America’s $72.5M settlement with Epstein accusers</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNHVyYkxUNjJhTDVwWVJ6ZUdZTjUzazFLdndxVlBJVVgzMXQtNWZFbHdpM2taYnJ3UFFJbWVucnBtQUM1bXVlNFNTRzlIczJfTFYwVm5GX2lmMnJlc05BNDA2QUVLRkp3ZUpTSW1kYUY5UlgwQ3BCaVhUaEdJRGpoeGktel8wNE1tbGNqZFp6NGpaWTdfOXF5T0RwQ2ZzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Maryland Daily Record</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr"/>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>f93b7abdfabcf569fd2cd94b</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>bab403c9efc026019d7c4cb0</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr"/>
-      <c r="AF14" s="2" t="inlineStr"/>
-      <c r="AG14" s="2" t="inlineStr"/>
-      <c r="AH14" s="2" t="inlineStr"/>
-      <c r="AI14" s="2" t="inlineStr"/>
-      <c r="AJ14" s="2" t="inlineStr"/>
-      <c r="AK14" s="2" t="inlineStr"/>
-      <c r="AL14" s="2" t="inlineStr"/>
-      <c r="AM14" s="2" t="inlineStr"/>
-      <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
-      <c r="AP14" s="2" t="inlineStr"/>
-      <c r="AQ14" s="2" t="inlineStr"/>
-      <c r="AR14" s="2" t="inlineStr"/>
-      <c r="AS14" s="2" t="inlineStr"/>
-      <c r="AT14" s="2" t="inlineStr"/>
-      <c r="AU14" s="2" t="inlineStr"/>
-      <c r="AV14" s="2" t="inlineStr"/>
-      <c r="AW14" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX14" s="2" t="inlineStr"/>
-      <c r="AY14" s="2" t="inlineStr"/>
-      <c r="AZ14" s="2" t="inlineStr"/>
-      <c r="BA14" s="2" t="inlineStr"/>
-      <c r="BB14" s="2" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="BC14" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="2" t="inlineStr"/>
-      <c r="BE14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH14"/>
+  <autoFilter ref="A1:BL11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7273,7 +7279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7336,6 +7342,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7639,6 +7649,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7654,33 +7684,33 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Robinhood Markets</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T10:27:00+08:00</t>
+          <t>2026-08-28T07:37:55+08:00</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Last minute penalty lifts Arkansas State women’s soccer past Stephen F. Austin</t>
+          <t>Mt. Hood National Forest expands closures as wildfires burn - Oregon Public Broadcasting</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>天災</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>僅紀錄</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -7705,7 +7735,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>'-0.059</t>
+          <t>'-0.535</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
@@ -7719,40 +7749,40 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRjk0ZUY1N1hGdU9XekZZNFVNLUtkZkNEdVpNZmZ4NF9tOFRWa29XeUw3TVNHdXpNTlc3dnJ2dk0wNGVkNi1FV3JTSzNLRzROLWFETjdhS2hQZTQzOEdxazVDd002Q01TWWczckFKdnpSaWZpRDJ4RjZlbFZDYVZMQ055ZmxGYkNpQ0hJTWpzdHZFSWJMTXpYR18zTXdzOEJ5Zktodjlsb2VnVzJPTVFJ0gHDAUFVX3lxTE55S0FtNkQxd3VieWVmUy1SemlTVXhEdE1nREZJUXlZUGZVYUtVcGZJWEk5VnV4a1Q0dmlPSzBFZDFzQXd3eEdHZXZKT1lTaS00RVE0VTl0cUdLc2I1TDIyUTVYRV93Zk1DQWNEQmJTT1ZCNVVkdFQ1ZjZhNk0xT3gxa1U0eUpvdUNmcmlocUNsWURyOUtKRTVib01VNk1jcDJHZU5MSUU5UC1qaWpwRGxoSElUeEU2NTdnc2pXNjdUZnBfSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5GQ3dOd0lVeWE4YmtlNUpBdXhaN0ZOUmhfSXRtX3Rad3lfWXdqcE5YdElyV2s5Nm1MNVVOX241NFl2cVJiMWV1Y2J3TFM1RWxReE9oc1M0VUoyUE43UWg2Qy1XX0M0eUE4NUpqSDJPRzVRN1hBbW9TNkhRV2lXdw?oc=5</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>K8 News | Jonesboro, Arkansas</t>
+          <t>Oregon Public Broadcasting - OPB</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NATURAL_DISASTER</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>penalty</t>
+          <t>wildfire</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>b0bafb43203fae7530132a60</t>
+          <t>e6010eef57b51356f9c95e66</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>44d610cecd4564b7ccd32929</t>
+          <t>b975509b6161afbd04e87c97</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr"/>
@@ -7784,7 +7814,7 @@
       <c r="BA2" s="2" t="inlineStr"/>
       <c r="BB2" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="BC2" s="2" t="inlineStr">
@@ -7794,194 +7824,28 @@
       </c>
       <c r="BD2" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="BE2" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Robinhood Markets</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28T07:37:55+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Mt. Hood National Forest expands closures as wildfires burn - Oregon Public Broadcasting</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.535</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5GQ3dOd0lVeWE4YmtlNUpBdXhaN0ZOUmhfSXRtX3Rad3lfWXdqcE5YdElyV2s5Nm1MNVVOX241NFl2cVJiMWV1Y2J3TFM1RWxReE9oc1M0VUoyUE43UWg2Qy1XX0M0eUE4NUpqSDJPRzVRN1hBbW9TNkhRV2lXdw?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Oregon Public Broadcasting - OPB</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>e6010eef57b51356f9c95e66</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>b975509b6161afbd04e87c97</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr"/>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH3"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7992,7 +7856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8055,6 +7919,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8358,9 +8226,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8371,7 +8259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8421,477 +8309,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="3" t="n">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="2" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="3" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-28.xlsx
+++ b/news_daily/2026-08-28.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1643,13 +1643,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1698,7 +1702,11 @@
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>9fb5d205be4747fd90e8e8a677aff733</t>
+        </is>
+      </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>28cd053747b867acc93804fe</t>
@@ -1719,7 +1727,11 @@
       <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="inlineStr"/>
       <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="inlineStr"/>
@@ -1765,8 +1777,16 @@
       <c r="BH6" s="4" t="inlineStr"/>
       <c r="BI6" s="4" t="inlineStr"/>
       <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2165,13 +2185,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -2220,7 +2244,11 @@
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>0333dcbfe6354e9587244117c8711990</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>bf7c7ad3b95b58efe84c4198</t>
@@ -2241,7 +2269,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -2287,8 +2319,16 @@
       <c r="BH9" s="4" t="inlineStr"/>
       <c r="BI9" s="4" t="inlineStr"/>
       <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2675,178 +2715,202 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>HPQ</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>HP Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-08-28T09:53:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>HPQ Q2 Deep Dive: AI PCs Drive Growth Amid Margin Pressures and Cautious Outlook</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.149</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcGw2YkZuTk9leEZSZXdhRVNRdFdBNjFBQXpnVFNzcVp5Qk9pNzUxdzFvR3dpMldJbEdRNTRLRllfaTJ4ejY0QmdUM213WkVyanMtZ0xXR0hRV0hmRlI1Q0EweUdBY0hrcm1hcTZPX1ZKd09NZnlQQndobkFvcS1aNHRFLWhmQjd5Yk5tZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>aa2f663c26ba4c279502701e8a86c562</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>8e75ff9786121fe28966481d</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>a44ba651f906be9b1d3a4bc9</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcGw2YkZuTk9leEZSZXdhRVNRdFdBNjFBQXpnVFNzcVp5Qk9pNzUxdzFvR3dpMldJbEdRNTRLRllfaTJ4ejY0QmdUM213WkVyanMtZ0xXR0hRV0hmRlI1Q0EweUdBY0hrcm1hcTZPX1ZKd09NZnlQQndobkFvcS1aNHRFLWhmQjd5Yk5tZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>8e75ff9786121fe28966481d</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>a44ba651f906be9b1d3a4bc9</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>HPQ</t>
         </is>
       </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="4" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr"/>
-      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3435,13 +3499,17 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -3490,7 +3558,11 @@
         </is>
       </c>
       <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>de8aeca90e61443f84b99674250b0dee</t>
+        </is>
+      </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
           <t>843cd612cdc5d8bcdd4f7c77</t>
@@ -3511,7 +3583,11 @@
       <c r="AL16" s="4" t="inlineStr"/>
       <c r="AM16" s="4" t="inlineStr"/>
       <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
+      <c r="AO16" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="4" t="inlineStr"/>
       <c r="AQ16" s="4" t="inlineStr"/>
       <c r="AR16" s="4" t="inlineStr"/>
@@ -3557,8 +3633,16 @@
       <c r="BH16" s="4" t="inlineStr"/>
       <c r="BI16" s="4" t="inlineStr"/>
       <c r="BJ16" s="4" t="inlineStr"/>
-      <c r="BK16" s="4" t="inlineStr"/>
-      <c r="BL16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3590,32 +3674,32 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3655,7 +3739,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -3664,7 +3748,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>7903bb70c9314f6991933e233abf09fa</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>e6010eef57b51356f9c95e66</t>
@@ -3687,7 +3775,7 @@
       <c r="AN17" s="2" t="inlineStr"/>
       <c r="AO17" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP17" s="2" t="inlineStr"/>
@@ -3729,10 +3817,22 @@
       </c>
       <c r="BG17" s="2" t="inlineStr"/>
       <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5016,7 +5116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL11"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5650,13 +5750,17 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -5705,7 +5809,11 @@
         </is>
       </c>
       <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>9fb5d205be4747fd90e8e8a677aff733</t>
+        </is>
+      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>28cd053747b867acc93804fe</t>
@@ -5726,7 +5834,11 @@
       <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="inlineStr"/>
       <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="inlineStr"/>
@@ -5772,8 +5884,16 @@
       <c r="BH3" s="4" t="inlineStr"/>
       <c r="BI3" s="4" t="inlineStr"/>
       <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr"/>
-      <c r="BL3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -5824,13 +5944,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -5879,7 +6003,11 @@
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>0333dcbfe6354e9587244117c8711990</t>
+        </is>
+      </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>bf7c7ad3b95b58efe84c4198</t>
@@ -5900,7 +6028,11 @@
       <c r="AL4" s="4" t="inlineStr"/>
       <c r="AM4" s="4" t="inlineStr"/>
       <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="4" t="inlineStr"/>
       <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="inlineStr"/>
@@ -5946,8 +6078,16 @@
       <c r="BH4" s="4" t="inlineStr"/>
       <c r="BI4" s="4" t="inlineStr"/>
       <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -6144,550 +6284,582 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>HPQ</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>HP Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-28T09:53:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>HPQ Q2 Deep Dive: AI PCs Drive Growth Amid Margin Pressures and Cautious Outlook</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T08:36:35+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Judge to consider final approval of Bank of America's $72 million settlement with Epstein accusers</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQOWV5V0VsYklTLVo0UjZGRExjNXhBd0tQTXRVSW00QnhJVmlLQlJWdENmUHBhWkJQc3pqMjItY1U4eU52clVKSS02VFpaZnBBOHZaZXF3R1JvZEZJWjREZXQ3T29DV2k4UVppSjN3bjJ1aHRMT0tUcjR0emlYNlhWSnh6SDg1QU42T1M5X1I4aS0xNWVIWEZJMU50U0ttWEdNaTgwZnJIOXE2Zm1obmFaaDB4aHVRT3NCWDRPczlOUjRLQVJEU25lbUE3N2tVVExDenhzU3pYamFpOC1xVWl6SGI3aw?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>ABC7 Bay Area</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>d64dfbc740c74153853e51db674196fa</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>36e90d082ca1e51c293bcd81</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>5d79e7490b12c1e27e991a8e</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcGw2YkZuTk9leEZSZXdhRVNRdFdBNjFBQXpnVFNzcVp5Qk9pNzUxdzFvR3dpMldJbEdRNTRLRllfaTJ4ejY0QmdUM213WkVyanMtZ0xXR0hRV0hmRlI1Q0EweUdBY0hrcm1hcTZPX1ZKd09NZnlQQndobkFvcS1aNHRFLWhmQjd5Yk5tZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>8e75ff9786121fe28966481d</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>a44ba651f906be9b1d3a4bc9</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>HPQ</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28T08:36:35+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Judge to consider final approval of Bank of America's $72 million settlement with Epstein accusers</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Starbucks Corporation</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T08:10:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Starbucks (SBUX)’s Corporate Layoffs Could Strengthen its Turnaround, But Risks Remain</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.686</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQOWV5V0VsYklTLVo0UjZGRExjNXhBd0tQTXRVSW00QnhJVmlLQlJWdENmUHBhWkJQc3pqMjItY1U4eU52clVKSS02VFpaZnBBOHZaZXF3R1JvZEZJWjREZXQ3T29DV2k4UVppSjN3bjJ1aHRMT0tUcjR0emlYNlhWSnh6SDg1QU42T1M5X1I4aS0xNWVIWEZJMU50U0ttWEdNaTgwZnJIOXE2Zm1obmFaaDB4aHVRT3NCWDRPczlOUjRLQVJEU25lbUE3N2tVVExDenhzU3pYamFpOC1xVWl6SGI3aw?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>ABC7 Bay Area</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>d64dfbc740c74153853e51db674196fa</t>
-        </is>
-      </c>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>36e90d082ca1e51c293bcd81</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>5d79e7490b12c1e27e991a8e</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOUlFUQUtYdG9KYzlfVTFXeHpsY2wwZzRHendmbEJkX2JxOGx3YTJXWlc4d1hTcTdRelRHOFRmMDVsdWpQTjZVODdxU0ticlE1YzFqSW5wTjhOR0xlT2RQSVVRNmN1RFVGTThTU1hSdEZVQi0tYS1ZdVNMSW9TanRhQlpkdXpiajZmbjVYblczVUVKYnNVQ3doY1V1czlxWWs1cG5ITVlR?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>de8aeca90e61443f84b99674250b0dee</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>843cd612cdc5d8bcdd4f7c77</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>2e750ae64f16765acb85ca7c</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr">
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Starbucks Corporation</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-28T08:10:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Starbucks (SBUX)’s Corporate Layoffs Could Strengthen its Turnaround, But Risks Remain</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28T03:45:22+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>PENTAIR CLASS ACTION ALERT: Bragar Eagel &amp; Squire, P.C.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxQOFZVeF9XRFNleFZJLUhSYkoxZUZISUdLUWk2NlBQdUd0V1k5V3h2TGNIREtMc3BjWG1rbnRodkc1alZRS2lUZ1M4cDlkZ2hqX0M3V3N3eTVEZjNKM2JZV1NQSDVwMU1aT3owRjFNQ0NmRWR1LWFiRGg2OE1PVVVYVm9leHJmYmtLdmNZTTR1c3R2WW9ydzFGcFBIYWcySktCdTV4LTZiV0ZqUUtfbzVwU0dVRWJhSmFyQm9VQnBubDRiRFVSd1YwOHY1UnNuOXpOcUktLS1WWE9NMXE2QWw5aWJnRDlfdzl5WWNJSEZEMmtXclNLWE0tS3diel9FQU8xakpqZHVvNmxVeW9RRWN1bVNuQ1hILXF3M0pLR0taSlVjN2NxblNDcnJFU0hqQ0tmS3hHaG9tbURhWEVqaTFZenFuSzY?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>ed31d2e466574160a597ad9bf2d66732</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>6620fc0f873a145ca08568af</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>becd80dd500a64133a6ce5b3</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>'-0.686</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOUlFUQUtYdG9KYzlfVTFXeHpsY2wwZzRHendmbEJkX2JxOGx3YTJXWlc4d1hTcTdRelRHOFRmMDVsdWpQTjZVODdxU0ticlE1YzFqSW5wTjhOR0xlT2RQSVVRNmN1RFVGTThTU1hSdEZVQi0tYS1ZdVNMSW9TanRhQlpkdXpiajZmbjVYblczVUVKYnNVQ3doY1V1czlxWWs1cG5ITVlR?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>843cd612cdc5d8bcdd4f7c77</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>2e750ae64f16765acb85ca7c</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -6702,22 +6874,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>GoDaddy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T03:45:22+08:00</t>
+          <t>2026-08-28T03:07:00+08:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>PENTAIR CLASS ACTION ALERT: Bragar Eagel &amp; Squire, P.C.</t>
+          <t>SueWallSt Reminds GoDaddy Inc. Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 20, 2026 - GDDY</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -6758,7 +6930,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>'-0.072</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
@@ -6772,12 +6944,12 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxQOFZVeF9XRFNleFZJLUhSYkoxZUZISUdLUWk2NlBQdUd0V1k5V3h2TGNIREtMc3BjWG1rbnRodkc1alZRS2lUZ1M4cDlkZ2hqX0M3V3N3eTVEZjNKM2JZV1NQSDVwMU1aT3owRjFNQ0NmRWR1LWFiRGg2OE1PVVVYVm9leHJmYmtLdmNZTTR1c3R2WW9ydzFGcFBIYWcySktCdTV4LTZiV0ZqUUtfbzVwU0dVRWJhSmFyQm9VQnBubDRiRFVSd1YwOHY1UnNuOXpOcUktLS1WWE9NMXE2QWw5aWJnRDlfdzl5WWNJSEZEMmtXclNLWE0tS3diel9FQU8xakpqZHVvNmxVeW9RRWN1bVNuQ1hILXF3M0pLR0taSlVjN2NxblNDcnJFU0hqQ0tmS3hHaG9tbURhWEVqaTFZenFuSzY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOWFNsdUU2TVVXU2t6djFQQlpqMFpfcWtXWnJHZ3NERzFGa0xzUWFEdlIybnpZNzFnVl9TOWxMa2M4N19GYXl0cW5GZU5nR25hZklFc09nUGtKY2FZSERlUEZyTDAtTHhOa1lBWjJITUl2ejhtTWc1MUxMZFpIMWx0WEp2T2d0VlktNnd0NVZpeE9kaUJ2NXVRNG9UQThRaVNGcDZVSVJOZ2c3ZEhGSjRyZDRhSVc2b01hN2RPeGRYZ3Y0U2d5QnRKWTlpdG5EWWtXNkkzTHR4Sk1OeU4yam1QSk1hZ3l1MjM1aVo4dzczVU91SC1xWnExdnBwOE5qYndjVzByTGRxN0VxZ3ZIUXJoazRVT2E0cWpVYW5Z?oc=5</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr"/>
@@ -6799,17 +6971,17 @@
       <c r="AA9" s="3" t="inlineStr"/>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>ed31d2e466574160a597ad9bf2d66732</t>
+          <t>fabca78aca8a431d83e275b9fc14d273</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>6620fc0f873a145ca08568af</t>
+          <t>a49c911a8ad6f60543b8b451</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>becd80dd500a64133a6ce5b3</t>
+          <t>3245a856ccbcb227925ccec7</t>
         </is>
       </c>
       <c r="AE9" s="3" t="inlineStr"/>
@@ -6834,14 +7006,18 @@
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="inlineStr"/>
       <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX9" s="3" t="inlineStr"/>
       <c r="AY9" s="3" t="inlineStr"/>
       <c r="AZ9" s="3" t="inlineStr"/>
       <c r="BA9" s="3" t="inlineStr"/>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="BC9" s="3" t="inlineStr">
@@ -6852,13 +7028,17 @@
       <c r="BD9" s="3" t="inlineStr"/>
       <c r="BE9" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG9" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
@@ -6888,22 +7068,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>GoDaddy Inc. Class A Common Stock</t>
+          <t>Bank of America Corporation Common Stock</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T03:07:00+08:00</t>
+          <t>2026-08-28T01:25:25+08:00</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>SueWallSt Reminds GoDaddy Inc. Investors of the Pending Class Action Lawsuit With a Lead Plaintiff Deadline of October 20, 2026 - GDDY</t>
+          <t>Court approves Bank of America’s $72.5M settlement with Epstein accusers</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -6944,7 +7124,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>'-0.072</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr"/>
@@ -6958,12 +7138,12 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOWFNsdUU2TVVXU2t6djFQQlpqMFpfcWtXWnJHZ3NERzFGa0xzUWFEdlIybnpZNzFnVl9TOWxMa2M4N19GYXl0cW5GZU5nR25hZklFc09nUGtKY2FZSERlUEZyTDAtTHhOa1lBWjJITUl2ejhtTWc1MUxMZFpIMWx0WEp2T2d0VlktNnd0NVZpeE9kaUJ2NXVRNG9UQThRaVNGcDZVSVJOZ2c3ZEhGSjRyZDRhSVc2b01hN2RPeGRYZ3Y0U2d5QnRKWTlpdG5EWWtXNkkzTHR4Sk1OeU4yam1QSk1hZ3l1MjM1aVo4dzczVU91SC1xWnExdnBwOE5qYndjVzByTGRxN0VxZ3ZIUXJoazRVT2E0cWpVYW5Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNHVyYkxUNjJhTDVwWVJ6ZUdZTjUzazFLdndxVlBJVVgzMXQtNWZFbHdpM2taYnJ3UFFJbWVucnBtQUM1bXVlNFNTRzlIczJfTFYwVm5GX2lmMnJlc05BNDA2QUVLRkp3ZUpTSW1kYUY5UlgwQ3BCaVhUaEdJRGpoeGktel8wNE1tbGNqZFp6NGpaWTdfOXF5T0RwQ2ZzUQ?oc=5</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Maryland Daily Record</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr"/>
@@ -6979,23 +7159,23 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>fabca78aca8a431d83e275b9fc14d273</t>
+          <t>8a938431d8f34286865149e1237129a0</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>a49c911a8ad6f60543b8b451</t>
+          <t>f93b7abdfabcf569fd2cd94b</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>3245a856ccbcb227925ccec7</t>
+          <t>bab403c9efc026019d7c4cb0</t>
         </is>
       </c>
       <c r="AE10" s="3" t="inlineStr"/>
@@ -7031,7 +7211,7 @@
       <c r="BA10" s="3" t="inlineStr"/>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="BC10" s="3" t="inlineStr">
@@ -7056,7 +7236,11 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="3" t="inlineStr"/>
       <c r="BK10" s="3" t="inlineStr">
         <is>
@@ -7069,206 +7253,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28T01:25:25+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Court approves Bank of America’s $72.5M settlement with Epstein accusers</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNHVyYkxUNjJhTDVwWVJ6ZUdZTjUzazFLdndxVlBJVVgzMXQtNWZFbHdpM2taYnJ3UFFJbWVucnBtQUM1bXVlNFNTRzlIczJfTFYwVm5GX2lmMnJlc05BNDA2QUVLRkp3ZUpTSW1kYUY5UlgwQ3BCaVhUaEdJRGpoeGktel8wNE1tbGNqZFp6NGpaWTdfOXF5T0RwQ2ZzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Maryland Daily Record</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>8a938431d8f34286865149e1237129a0</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>f93b7abdfabcf569fd2cd94b</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>bab403c9efc026019d7c4cb0</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL11"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7279,7 +7265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7670,182 +7656,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Robinhood Markets</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28T07:37:55+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Mt. Hood National Forest expands closures as wildfires burn - Oregon Public Broadcasting</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.535</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5GQ3dOd0lVeWE4YmtlNUpBdXhaN0ZOUmhfSXRtX3Rad3lfWXdqcE5YdElyV2s5Nm1MNVVOX241NFl2cVJiMWV1Y2J3TFM1RWxReE9oc1M0VUoyUE43UWg2Qy1XX0M0eUE4NUpqSDJPRzVRN1hBbW9TNkhRV2lXdw?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Oregon Public Broadcasting - OPB</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>e6010eef57b51356f9c95e66</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>b975509b6161afbd04e87c97</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-28.xlsx
+++ b/news_daily/2026-08-28.xlsx
@@ -1078,28 +1078,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1139,7 +1143,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1148,7 +1152,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>37b1aed19602495a9cf60a925e5fa7d2</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>12d92439e62c23b1475061c7</t>
@@ -1169,7 +1177,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1205,10 +1217,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1837,13 +1861,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1892,7 +1920,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>3f37c31f74624c1e9c3fb94369831cdd</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>59f6e258cf159c82c3472ab9</t>
@@ -1913,7 +1945,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1959,8 +1995,16 @@
       <c r="BH7" s="2" t="inlineStr"/>
       <c r="BI7" s="2" t="inlineStr"/>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2011,13 +2055,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2066,7 +2114,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>b3d0191fabef43b8b9d2141610cb1332</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>539e65b6f9a2efcc9136ed8f</t>
@@ -2087,7 +2139,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2133,8 +2189,16 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -3144,28 +3208,32 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3205,7 +3273,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -3214,7 +3282,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>3804452bb9024ee780ae270d32842f62</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>2424b34306368eb06f679e95</t>
@@ -3235,7 +3307,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3271,10 +3347,22 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3310,28 +3398,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3371,7 +3463,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3380,7 +3472,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>4ad77bc1920c47edb29e7022e51bb5d6</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>8bc109c1134c436c0d9d07af</t>
@@ -3401,7 +3497,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3445,10 +3545,22 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3883,13 +3995,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3934,7 +4050,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>67ef514bd6e846469a09051cebe30d68</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>6e1b34a863bc78854e48b08e</t>
@@ -3955,7 +4075,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4001,8 +4125,16 @@
       <c r="BH18" s="2" t="inlineStr"/>
       <c r="BI18" s="2" t="inlineStr"/>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4038,28 +4170,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4099,7 +4235,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4108,7 +4244,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>d254dab2b22a4d548364a7f5b8609c70</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>b27b85e62bf984917679535b</t>
@@ -4129,7 +4269,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4173,10 +4317,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4592,28 +4748,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4653,7 +4813,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4662,7 +4822,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>5cd714f9c35b4c5bb69fc1a3ed23bf7c</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>017a9cfcce3c6f153b2ec826</t>
@@ -4683,7 +4847,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4727,10 +4895,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4766,28 +4946,32 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4827,7 +5011,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -4836,7 +5020,11 @@
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>ee80a5342bc0476fa578199821b86e9c</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>5991a77c93e8edc6aab8c90f</t>
@@ -4857,7 +5045,11 @@
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr"/>
       <c r="AN23" s="2" t="inlineStr"/>
-      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="2" t="inlineStr"/>
       <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
@@ -4901,10 +5093,22 @@
         </is>
       </c>
       <c r="BH23" s="2" t="inlineStr"/>
-      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
